--- a/Intern_Exam_Portal/sample_mcqs.xlsx
+++ b/Intern_Exam_Portal/sample_mcqs.xlsx
@@ -426,76 +426,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>question</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>option_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>option_b</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>option_c</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>option_d</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>correct_answer</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>question_mark</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>What does HTML stand for?</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>HyperText Markup Language</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>HighText Machine Language</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>HyperText and links Markup Language</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>None of the above</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -504,30 +521,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Which language is used for styling web pages?</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CSS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>b</t>
         </is>
@@ -536,30 +558,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>What does CSS stand for?</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Computer Style Sheets</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Creative Style Sheets</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Cascading Style Sheets</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Colorful Style Sheets</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -568,30 +595,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Which HTML tag is used for the largest heading?</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>&lt;h6&gt;</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>&lt;heading&gt;</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>&lt;h1&gt;</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>&lt;head&gt;</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -600,30 +632,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>What is the correct HTML element for inserting a line break?</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>&lt;br&gt;</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>&lt;lb&gt;</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>&lt;break&gt;</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>&lt;newline&gt;</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -632,30 +669,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Which symbol is used for comments in Python?</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>/*</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -664,30 +706,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>What does SQL stand for?</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Structured Query Language</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Simple Query Language</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Standard Question Language</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Structured Question Language</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -696,30 +743,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Which data type stores decimal numbers in Python?</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>str</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>b</t>
         </is>
@@ -728,30 +780,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>What is a primary key in a database?</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>A key for locking the database</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>A unique identifier for each record</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>The first column</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>An index column</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>b</t>
         </is>
@@ -760,30 +817,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Networking</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Which HTTP method is used to send data to a server?</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -792,30 +854,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>What does API stand for?</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Application Programming Integration</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Application Protocol Interface</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Application Programming Interface</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Automated Program Interface</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -824,30 +891,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>Which of the following is NOT a JavaScript framework?</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>React</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Angular</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Vue</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Django</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -856,30 +928,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>What is a REST API?</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>A type of database</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>A protocol for file transfer</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>An architectural style for APIs over HTTP</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>A JavaScript framework</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -888,30 +965,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>What does OOP stand for?</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Object Oriented Programming</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Open Oriented Protocol</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Object Output Process</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>None of the above</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -920,30 +1002,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Which Python keyword is used to create a function?</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>function</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>define</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>def</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>func</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -952,30 +1039,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>What is Git used for?</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Database management</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Version control</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Web development</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>API testing</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>b</t>
         </is>
@@ -984,30 +1076,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Which tag is used to create a hyperlink in HTML?</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>&lt;link&gt;</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>&lt;a&gt;</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>&lt;href&gt;</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>&lt;url&gt;</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>b</t>
         </is>
@@ -1016,30 +1113,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Algorithm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>What is the time complexity of binary search?</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>O(n)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>O(n²)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>O(log n)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>O(1)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -1048,30 +1150,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Which of these is a NoSQL database?</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>MongoDB</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>SQLite</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -1080,30 +1187,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>What does JSON stand for?</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>JavaScript Object Numbers</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>JavaScript Object Notation</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Java Source Object Network</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>JavaScript Output Notation</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>b</t>
         </is>
@@ -1112,30 +1224,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Which command is used to install Python packages?</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>npm install</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>pip install</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>apt install</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>brew install</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>b</t>
         </is>
@@ -1144,30 +1261,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>What is a virtual environment in Python?</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>A cloud server</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>An isolated Python environment</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>A Docker container</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>A virtual machine</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>b</t>
         </is>
@@ -1176,30 +1298,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Networking</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Which HTTP status code means 'Not Found'?</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>401</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -1208,30 +1335,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>What is the purpose of an index in a database?</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>To encrypt data</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>To backup data</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>To speed up data retrieval</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>To delete data</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -1240,32 +1372,105 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Which of the following is a Python web framework?</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>React</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Angular</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>FastAPI</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Vue</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Describe Object-Oriented Programming in Python and its four main principles.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5M</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Explain the difference between INNER JOIN and LEFT JOIN with an example.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5M</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>What is the difference between a stack and a queue? Give a real-world example for each.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Algorithm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Describe the steps involved in the Software Development Life Cycle (SDLC).</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>10M</t>
         </is>
       </c>
     </row>
